--- a/Reglas del negocio.xlsx
+++ b/Reglas del negocio.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3600414ad120ecfd/Documentos/GitHub/CLINIDENT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatDosuki\Documents\GitHub\CLINIDENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17B3E463-F4FC-4E46-A9C9-CADF6AD80480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="142">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -159,12 +158,6 @@
     <t>SKH003-03</t>
   </si>
   <si>
-    <t>Auditoría de Cita y Facturación Integrada</t>
-  </si>
-  <si>
-    <t>Al inspeccionar el detalle de una cita, el sistema recupera la información agendada y la cruza automáticamente con la base de datos contable para mostrar el diagnóstico y el costo total pagado</t>
-  </si>
-  <si>
     <t>Garantizar la transparencia y coherencia entre la atención médica y su facturación.</t>
   </si>
   <si>
@@ -177,9 +170,6 @@
     <t>Cálculo selectivo de impuestos</t>
   </si>
   <si>
-    <t>Los impuestos se calculan sobre el valor después del descuento dependiendo del servicio</t>
-  </si>
-  <si>
     <t>Cumplir con la normativa contable vigente.</t>
   </si>
   <si>
@@ -189,9 +179,6 @@
     <t>Restricción temporal progresiva y sugerencia de cambio</t>
   </si>
   <si>
-    <t>Al superar los 3 intentos fallidos, el sistema congela temporalmente la opción de ingreso por 30 segundos y muestra el enlace de recuperación..</t>
-  </si>
-  <si>
     <t>Mitigar ataques automatizados sin bloquear la cuenta del usuario..</t>
   </si>
   <si>
@@ -219,9 +206,6 @@
     <t>No se podrá eliminar información clínica de forma permanente.</t>
   </si>
   <si>
-    <t>Los registros clínicos solo podrán marcarse como inactivos (eliminación lógica).</t>
-  </si>
-  <si>
     <t>Garantizar trazabilidad y respaldo histórico.</t>
   </si>
   <si>
@@ -231,25 +215,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>Cálculo obligatorio del total</t>
-  </si>
-  <si>
-    <t>El total debe calcularse antes de emitir la factura</t>
-  </si>
-  <si>
-    <t>Asegurar exactitud en la facturación</t>
-  </si>
-  <si>
-    <t>El sistema bloquea la emisión de la factura si no se calcula el total.</t>
-  </si>
-  <si>
     <t>R5</t>
   </si>
   <si>
     <t>Factura con tratamientos obligatorios</t>
-  </si>
-  <si>
-    <t>Una factura debe contener al menos un tratamiento registrado.</t>
   </si>
   <si>
     <t>Evitar facturas vacías o inválidas.</t>
@@ -349,18 +318,6 @@
     <t>creacion de usuarios - 007</t>
   </si>
   <si>
-    <t>Restricción local de intentos de verificación</t>
-  </si>
-  <si>
-    <t>El sistema valida que el código introducido por el usuario sea idéntico al código estático del código fuente.</t>
-  </si>
-  <si>
-    <t>Evitar registros forzados con datos inválidos.</t>
-  </si>
-  <si>
-    <t>Solicitud rechazada y alerta en pantalla si no coincide.</t>
-  </si>
-  <si>
     <t>R9</t>
   </si>
   <si>
@@ -388,9 +345,6 @@
     <t>Formulario inicializado con datos del paciente y procedimiento elegido de la lista.</t>
   </si>
   <si>
-    <t>creacion de usuarios - 008</t>
-  </si>
-  <si>
     <t>El sistema debe confirmar el registro del usuario</t>
   </si>
   <si>
@@ -421,9 +375,6 @@
     <t>confirmación de cita</t>
   </si>
   <si>
-    <t>Toda solicitud aprobada de horario por el usuario es confirmada y registrada por el sistema.Toda solicitud aprobada de horario por el usuario es confirmada y registrada por el sistema.</t>
-  </si>
-  <si>
     <t>formalizar el compromiso entre el usuario y el servicio</t>
   </si>
   <si>
@@ -479,12 +430,33 @@
   </si>
   <si>
     <t>el sistema llega a su estado fin</t>
+  </si>
+  <si>
+    <t>Al superar los 3 intentos fallidos, el sistema congela temporalmente la opción de ingreso por 10 segundos y muestra el enlace de recuperación..</t>
+  </si>
+  <si>
+    <t>Toda solicitud aprobada de horario por el usuario es confirmada y registrada por el sistema.</t>
+  </si>
+  <si>
+    <t>Los impuestos se calculan sobre el valor dependiendo del servicio</t>
+  </si>
+  <si>
+    <t>Una factura debe contener un tratamiento registrado.</t>
+  </si>
+  <si>
+    <t>Estado de pago de cita</t>
+  </si>
+  <si>
+    <t>Al mostrarse las citas, el sistema recupera la información agendada y la cruza automáticamente con la base de datos contable para mostrar el estado de pago</t>
+  </si>
+  <si>
+    <t>Los registros clínicos no pódran ser eliminados</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -686,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -773,6 +745,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,7 +965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1172,16 +1150,16 @@
         <v>33</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="X3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="118.5" customHeight="1">
@@ -1218,146 +1196,145 @@
       <c r="M4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="25" t="s">
+      <c r="N4" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="P4" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="Q4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="U4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>68</v>
+      <c r="V4" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="X4" s="16" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y4" s="16" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="93" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="H5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="I5" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="J5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="K5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="M5" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="N5" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="P5" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="Q5" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="29" t="s">
+      <c r="U5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="P5" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="V5" s="16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="W5" s="16" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="X5" s="16" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Y5" s="16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="76.5" customHeight="1">
       <c r="A6" s="30" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="M6" s="29"/>
       <c r="N6" s="29"/>
-      <c r="O6" s="20"/>
       <c r="P6" s="29"/>
       <c r="Q6" s="29"/>
       <c r="U6" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" s="16" t="s">
-        <v>83</v>
+        <v>91</v>
+      </c>
+      <c r="V6" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="W6" s="16" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="Y6" s="16" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="120">
@@ -1367,19 +1344,19 @@
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="G7" s="20" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M7" s="29"/>
       <c r="N7" s="29"/>
@@ -1387,22 +1364,22 @@
       <c r="P7" s="29"/>
       <c r="Q7" s="29"/>
       <c r="U7" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="V7" s="16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="W7" s="16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="X7" s="16" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Y7" s="16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="90">
+    <row r="8" spans="1:25" ht="75">
       <c r="A8" s="35" t="s">
         <v>1</v>
       </c>
@@ -1418,20 +1395,20 @@
       <c r="E8" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="I8" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="J8" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="K8" s="33" t="s">
         <v>109</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>110</v>
       </c>
       <c r="M8" s="29"/>
       <c r="N8" s="29"/>
@@ -1439,19 +1416,19 @@
       <c r="P8" s="29"/>
       <c r="Q8" s="29"/>
       <c r="U8" s="15" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="V8" s="21" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="W8" s="16" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="X8" s="16" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Y8" s="16" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="90">
@@ -1459,164 +1436,133 @@
         <v>14</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>124</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G9" s="20"/>
       <c r="M9" s="29"/>
       <c r="N9" s="29"/>
       <c r="O9" s="20"/>
       <c r="P9" s="29"/>
       <c r="Q9" s="29"/>
       <c r="U9" s="15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="V9" s="16" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="Y9" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="75">
+      <c r="A10" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" ht="150">
-      <c r="A10" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>130</v>
-      </c>
       <c r="C10" s="37" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="G10" s="20"/>
+        <v>117</v>
+      </c>
       <c r="M10" s="29"/>
       <c r="N10" s="29"/>
       <c r="O10" s="29"/>
       <c r="P10" s="29"/>
       <c r="Q10" s="29"/>
       <c r="U10" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="V10" s="21" t="s">
-        <v>126</v>
+        <v>62</v>
+      </c>
+      <c r="V10" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="X10" s="16" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="Y10" s="16" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="90">
       <c r="A11" s="36" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="V11" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="X11" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y11" s="16" t="s">
-        <v>138</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="U11" s="15"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
     </row>
     <row r="12" spans="1:25" ht="75">
       <c r="A12" s="36" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="U12" s="39"/>
     </row>
     <row r="13" spans="1:25" ht="60">
       <c r="A13" s="36" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="U13" s="39"/>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="U14" s="39"/>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="V15" s="16"/>
+        <v>134</v>
+      </c>
+      <c r="V13" s="16"/>
     </row>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -2600,6 +2546,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>